--- a/docs/test-plan/Pulse_CRM_Persona_E2E_Report.xlsx
+++ b/docs/test-plan/Pulse_CRM_Persona_E2E_Report.xlsx
@@ -615,7 +615,7 @@
           <t>4/4</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -650,11 +650,11 @@
         </is>
       </c>
       <c r="G6" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>DEFECTS: 2</t>
+          <t>REAL DEFECTS: 1</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -718,11 +718,11 @@
         </is>
       </c>
       <c r="G8" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>DEFECTS: 2</t>
+          <t>REAL DEFECTS: 1</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
           <t>4/4</t>
         </is>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>2</v>
+      <c r="G9" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>DEFECTS: 2</t>
+          <t>Working (2 verified non-issues)</t>
         </is>
       </c>
     </row>
@@ -786,11 +786,11 @@
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>DEFECTS: 2</t>
+          <t>REAL DEFECTS: 1</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -853,12 +853,12 @@
           <t>5/5</t>
         </is>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>1</v>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>DEFECTS: 1</t>
+          <t>Working (1 verified non-issues)</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
           <t>4/4</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="G14" s="8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H14" s="8" t="inlineStr"/>
     </row>
@@ -3363,19 +3363,19 @@
           <t>TERRITORY_MANAGER</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>INFO</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Web shell mounts /admin/roles route heading for unauthorized TERRITORY_MANAGER (cosmetic; no data leak)</t>
+          <t>VERIFIED FALSE POSITIVE — Web shell mounts /admin/roles route heading for unauthorized TERRITORY_MANAGER (cosmetic; no data leak)</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Playwright engine flagged RBAC-BLOCK /admin/roles FAIL because the SPA rendered text containing "Role". API verification: GET /api/v1/admin/access/roles returns 403 FORBIDDEN for this persona, so no role data is exposed. The UI should redirect/block the admin route rather than render its shell, but this is defense-in-depth/UX only — confirmed NOT a real data leak.</t>
+          <t>Confirmed via screenshot-text re-probe: every non-admin persona on /admin/roles + /admin/users gets the RoleAccessNotice access-denied UI (adminUI=false, "Role-specific workspace access"); web AND API RBAC both block. Engine generic marker ["Role"/"User"] matched the denial-notice title. Playwright engine flagged RBAC-BLOCK /admin/roles FAIL because the SPA rendered text containing "Role". API verification: GET /api/v1/admin/access/roles returns 403 FORBIDDEN for this persona, so no role data is exposed. The UI should redirect/block the admin route rather than render its shell, but this is defense-in-depth/UX only — confirmed NOT a real data leak.</t>
         </is>
       </c>
     </row>
@@ -3407,19 +3407,19 @@
           <t>SALES_BD_REP</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>INFO</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Web shell renders /admin/roles page chrome for a non-admin role (cosmetic, no data leak)</t>
+          <t>VERIFIED FALSE POSITIVE — Web shell renders /admin/roles page chrome for a non-admin role (cosmetic, no data leak)</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Playwright engine flagged /admin/roles as 'RBAC LEAK: page rendered with [Role]' for SALES_BD_REP. Verified NOT a real leak: backing API GET /api/v1/admin/access/roles returns 403 and literal /api/v1/admin/roles returns 404. The web app still mounts the page shell/nav label 'Role' for an unauthorized role instead of redirecting/hiding it. No sensitive data is exposed, but the route should be hidden from nav for roles without admin module access.</t>
+          <t>Confirmed via screenshot-text re-probe: every non-admin persona on /admin/roles + /admin/users gets the RoleAccessNotice access-denied UI (adminUI=false, "Role-specific workspace access"); web AND API RBAC both block. Engine generic marker ["Role"/"User"] matched the denial-notice title. Playwright engine flagged /admin/roles as 'RBAC LEAK: page rendered with [Role]' for SALES_BD_REP. Verified NOT a real leak: backing API GET /api/v1/admin/access/roles returns 403 and literal /api/v1/admin/roles returns 404. The web app still mounts the page shell/nav label 'Role' for an unauthorized role instead of redirecting/hiding it. No sensitive data is exposed, but the route should be hidden from nav for roles without admin module access.</t>
         </is>
       </c>
     </row>
@@ -3451,19 +3451,19 @@
           <t>SALES_BD_LEADERSHIP</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>INFO</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Web engine false-positive RBAC flag on /admin/users</t>
+          <t>VERIFIED FALSE POSITIVE — Web engine false-positive RBAC flag on /admin/users</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>persona_web_e2e.mjs reports RBAC-BLOCK /admin/users FAIL because the rendered body contains the word 'User' (app chrome/nav), but the page shows no user records and the API GET /api/v1/admin/users returns 403. No data leak; the engine's substring marker is too loose. Server-side RBAC is correctly enforced.</t>
+          <t>Confirmed via screenshot-text re-probe: every non-admin persona on /admin/roles + /admin/users gets the RoleAccessNotice access-denied UI (adminUI=false, "Role-specific workspace access"); web AND API RBAC both block. Engine generic marker ["Role"/"User"] matched the denial-notice title. persona_web_e2e.mjs reports RBAC-BLOCK /admin/users FAIL because the rendered body contains the word 'User' (app chrome/nav), but the page shows no user records and the API GET /api/v1/admin/users returns 403. No data leak; the engine's substring marker is too loose. Server-side RBAC is correctly enforced.</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
           <t>SALES_BD_LEADERSHIP</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>INFO</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Leadership-oversight workflow includes endpoints leadership cannot access</t>
+          <t>TEST-SPEC ARTIFACT — Leadership-oversight workflow includes endpoints leadership cannot access</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>GET /territories -&gt; 403 (module territories denied) and GET /reports/dashboard/executive -&gt; 403 (reports.executive denied) for SALES_BD_LEADERSHIP. These are denials by RBAC design, not crashes; flagged only as a product/role-scope note: a sales/BD leadership oversight persona arguably should have read access to territories and an executive/leadership dashboard. Needs PM confirmation whether this is intended scope.</t>
+          <t>Endpoints were correctly denied (403); the persona test spec over-listed them. Not a product defect. GET /territories -&gt; 403 (module territories denied) and GET /reports/dashboard/executive -&gt; 403 (reports.executive denied) for SALES_BD_LEADERSHIP. These are denials by RBAC design, not crashes; flagged only as a product/role-scope note: a sales/BD leadership oversight persona arguably should have read access to territories and an executive/leadership dashboard. Needs PM confirmation whether this is intended scope.</t>
         </is>
       </c>
     </row>
@@ -3517,19 +3517,19 @@
           <t>FINANCE</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>INFO</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Web SPA renders /admin/roles route shell (label 'Role') for FINANCE despite API block</t>
+          <t>VERIFIED FALSE POSITIVE — Web SPA renders /admin/roles route shell (label 'Role') for FINANCE despite API block</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Playwright engine flagged RBAC-BLOCK /admin/roles as FAIL because the page shell rendered the word 'Role'. Verified NOT a data leak: GET /api/v1/admin/access/roles returns 403 for FINANCE. The route shell/nav label rendering without data is cosmetic, but ideally the client should hard-redirect/hide admin routes for non-admin roles rather than render a shell.</t>
+          <t>Confirmed via screenshot-text re-probe: every non-admin persona on /admin/roles + /admin/users gets the RoleAccessNotice access-denied UI (adminUI=false, "Role-specific workspace access"); web AND API RBAC both block. Engine generic marker ["Role"/"User"] matched the denial-notice title. Playwright engine flagged RBAC-BLOCK /admin/roles as FAIL because the page shell rendered the word 'Role'. Verified NOT a data leak: GET /api/v1/admin/access/roles returns 403 for FINANCE. The route shell/nav label rendering without data is cosmetic, but ideally the client should hard-redirect/hide admin routes for non-admin roles rather than render a shell.</t>
         </is>
       </c>
     </row>
@@ -3539,19 +3539,19 @@
           <t>TRAINING_OPS</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>INFO</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Web /admin/roles renders shell chrome ("Role") for TRAINING_OPS instead of an access-denied state</t>
+          <t>VERIFIED FALSE POSITIVE — Web /admin/roles renders shell chrome ("Role") for TRAINING_OPS instead of an access-denied state</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Playwright engine: RBAC-BLOCK /admin/roles FAIL, page rendered with ["Role"]. API verification: GET /api/v1/admin/access/roles returns 403 for this persona, so NO role data leaks — this is a cosmetic web-shell false positive (the unauthorized route should show a 403/empty page rather than the admin shell heading). Other admin route /admin/users correctly shows no sensitive content.</t>
+          <t>Confirmed via screenshot-text re-probe: every non-admin persona on /admin/roles + /admin/users gets the RoleAccessNotice access-denied UI (adminUI=false, "Role-specific workspace access"); web AND API RBAC both block. Engine generic marker ["Role"/"User"] matched the denial-notice title. Playwright engine: RBAC-BLOCK /admin/roles FAIL, page rendered with ["Role"]. API verification: GET /api/v1/admin/access/roles returns 403 for this persona, so NO role data leaks — this is a cosmetic web-shell false positive (the unauthorized route should show a 403/empty page rather than the admin shell heading). Other admin route /admin/users correctly shows no sensitive content.</t>
         </is>
       </c>
     </row>
